--- a/attached_assets/list_books_for_create description.xlsx
+++ b/attached_assets/list_books_for_create description.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\b_outside\a_intesa_global_technology\Storify\Storify-Insights\Storify-Insights\attached_assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D1AD41-7BC4-420B-A80D-1436A60A7FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C5EB94-FC98-4A28-9544-6CE95401AE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{61CDC90C-EC06-4A7D-B103-BEBAB272D490}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{61CDC90C-EC06-4A7D-B103-BEBAB272D490}"/>
   </bookViews>
   <sheets>
     <sheet name="list_books" sheetId="1" r:id="rId1"/>
